--- a/doctool/test/auto/scenario33/システム機能設計書_サンプル_S33_expected.xlsx
+++ b/doctool/test/auto/scenario33/システム機能設計書_サンプル_S33_expected.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJ\01.Nablarch\repo\review-support-tool\doctool\test\temp_dir\scenario32\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PJ\01.Nablarch\repo\review-support-tool\doctool\test\temp_dir\scenario33\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CC4FEB4-5B37-4CBC-9B2C-AF5000B37408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92AF0AF8-585F-4C7F-AEF7-D2BBBF17AE89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="38700" windowHeight="15345" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4290" yWindow="4290" windowWidth="38700" windowHeight="15345" tabRatio="822" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="エラーシート" sheetId="11" r:id="rId1"/>
@@ -1262,7 +1262,7 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>システム機能設計書_サンプル_S32</t>
+    <t>システム機能設計書_サンプル_S33</t>
   </si>
   <si>
     <t>山田　太郎</t>
@@ -3269,7 +3269,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89586B3D-D90B-4859-BE85-107CD0A11F58}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E39E711A-AA82-4191-83E5-D6E4E9DEFBE2}">
   <sheetPr codeName="ErrorSheetTemplate">
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
@@ -3313,8 +3313,8 @@
   </sheetData>
   <phoneticPr fontId="10"/>
   <hyperlinks>
-    <hyperlink ref="B3" location="'変更履歴'!$E$35" display="'変更履歴'!$E$35" xr:uid="{F2BC86F3-7091-4682-B2E8-0C3C717AB28F}"/>
-    <hyperlink ref="B4" location="'2. WA1020101(プロジェクト登録画面)'!$E$65" display="'2. WA1020101(プロジェクト登録画面)'!$E$65" xr:uid="{90C95935-6A66-42A6-8430-5DD270B5FD1B}"/>
+    <hyperlink ref="B3" location="'変更履歴'!$E$35" display="'変更履歴'!$E$35" xr:uid="{2F6D269B-7F16-44F0-9DAD-F505822C166A}"/>
+    <hyperlink ref="B4" location="'2. WA1020101(プロジェクト登録画面)'!$E$65" display="'2. WA1020101(プロジェクト登録画面)'!$E$65" xr:uid="{91E8E690-72C9-4D2F-A22A-164300D38DEB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3461,7 +3461,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC22CE4F-6C34-4A9A-A97A-BDEDAA5D12CB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14854527-208D-488C-9D9E-0F4B02900C27}">
   <sheetPr codeName="SheetTemplate">
     <tabColor indexed="44"/>
     <pageSetUpPr fitToPage="1"/>
@@ -4084,16 +4084,16 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:K20" xr:uid="{724AA265-F57A-4B79-AF12-6D4221AD84DC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K15:K20" xr:uid="{2219AEAE-9A7F-41A1-86A5-6646AC63075D}">
       <formula1>"未,済"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="B15" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{292F15A6-9F6A-4EBC-AF47-4F12D0595B94}"/>
-    <hyperlink ref="B16" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{855E9C4D-8064-42BF-A0D1-8EC0098A8818}"/>
-    <hyperlink ref="B17" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{6C238A68-C29C-4277-A2AA-6A45D29B5F44}"/>
-    <hyperlink ref="B18" location="'2. WA1020101(プロジェクト登録画面)'!$E$63" display="'2. WA1020101(プロジェクト登録画面)'!$E$63" xr:uid="{5918D184-E457-455B-B410-E8CFA1B5554E}"/>
-    <hyperlink ref="B19" location="'2. WA1020101(プロジェクト登録画面)'!$E$64" display="'2. WA1020101(プロジェクト登録画面)'!$E$64" xr:uid="{FF87EB3F-B6AE-4A95-9C89-5D77D9551576}"/>
+    <hyperlink ref="B15" location="'2. WA1020101(プロジェクト登録画面)'!$B$5" display="'2. WA1020101(プロジェクト登録画面)'!$B$5" xr:uid="{0FD501DB-76F0-4039-96D1-C535474FC328}"/>
+    <hyperlink ref="B16" location="'2. WA1020101(プロジェクト登録画面)'!$E$60" display="'2. WA1020101(プロジェクト登録画面)'!$E$60" xr:uid="{94D371F7-9CE6-4A0E-BE5E-EBDC247C56D2}"/>
+    <hyperlink ref="B17" location="'2. WA1020101(プロジェクト登録画面)'!$E$62" display="'2. WA1020101(プロジェクト登録画面)'!$E$62" xr:uid="{EC81D520-FF6D-43E0-9D8F-E721E3CF3070}"/>
+    <hyperlink ref="B18" location="'2. WA1020101(プロジェクト登録画面)'!$E$63" display="'2. WA1020101(プロジェクト登録画面)'!$E$63" xr:uid="{88D9A15B-6F6F-4D35-813E-207F84757011}"/>
+    <hyperlink ref="B19" location="'2. WA1020101(プロジェクト登録画面)'!$E$64" display="'2. WA1020101(プロジェクト登録画面)'!$E$64" xr:uid="{15248D1E-16C6-4FA5-B52B-EE73528C4B61}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
   <pageSetup paperSize="9" scale="86" orientation="landscape" verticalDpi="200" r:id="rId1"/>
